--- a/Team-Data/2014-15/3-23-2014-15.xlsx
+++ b/Team-Data/2014-15/3-23-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -751,16 +818,16 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
@@ -787,7 +854,7 @@
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.443</v>
+        <v>0.435</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="J3" t="n">
-        <v>88.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="n">
         <v>8.1</v>
       </c>
       <c r="M3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O3" t="n">
         <v>14.9</v>
@@ -882,13 +949,13 @@
         <v>19.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R3" t="n">
         <v>11.3</v>
       </c>
       <c r="S3" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
         <v>44.1</v>
@@ -897,7 +964,7 @@
         <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W3" t="n">
         <v>8</v>
@@ -912,28 +979,28 @@
         <v>21.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AD3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH3" t="n">
         <v>10</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>13</v>
@@ -951,13 +1018,13 @@
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
@@ -975,16 +1042,16 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
@@ -993,7 +1060,7 @@
         <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.42</v>
+        <v>0.426</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
@@ -1043,43 +1110,43 @@
         <v>37.1</v>
       </c>
       <c r="J4" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.324</v>
+        <v>0.328</v>
       </c>
       <c r="O4" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S4" t="n">
         <v>31.9</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1091,25 +1158,25 @@
         <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA4" t="n">
         <v>20.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
@@ -1121,7 +1188,7 @@
         <v>19</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
@@ -1136,25 +1203,25 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
@@ -1169,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
         <v>15</v>
@@ -1178,7 +1245,7 @@
         <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -1207,97 +1274,97 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.435</v>
+        <v>0.441</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J5" t="n">
         <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.424</v>
+        <v>0.425</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.316</v>
+        <v>0.314</v>
       </c>
       <c r="O5" t="n">
         <v>17.2</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T5" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U5" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V5" t="n">
         <v>11.9</v>
       </c>
       <c r="W5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y5" t="n">
         <v>5.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
         <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1336,7 +1403,7 @@
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,16 +1415,16 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>0.597</v>
+        <v>0.592</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1407,19 +1474,19 @@
         <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.44</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O6" t="n">
         <v>19.9</v>
@@ -1428,13 +1495,13 @@
         <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R6" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S6" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T6" t="n">
         <v>45.9</v>
@@ -1443,7 +1510,7 @@
         <v>21.7</v>
       </c>
       <c r="V6" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="W6" t="n">
         <v>6</v>
@@ -1458,19 +1525,19 @@
         <v>18.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB6" t="n">
         <v>100.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1479,19 +1546,19 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
         <v>17</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
         <v>16</v>
@@ -1503,13 +1570,13 @@
         <v>2</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>5</v>
@@ -1521,16 +1588,16 @@
         <v>16</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1539,7 +1606,7 @@
         <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1676,10 +1743,10 @@
         <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1703,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1715,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" t="n">
         <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.629</v>
+        <v>0.62</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,10 +1838,10 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L8" t="n">
         <v>9.300000000000001</v>
@@ -1783,31 +1850,31 @@
         <v>26.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P8" t="n">
         <v>22.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U8" t="n">
         <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
@@ -1822,28 +1889,28 @@
         <v>19.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
       <c r="AC8" t="n">
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1864,7 +1931,7 @@
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
         <v>18</v>
@@ -1876,7 +1943,7 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
@@ -1891,13 +1958,13 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -2028,16 +2095,16 @@
         <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM9" t="n">
         <v>13</v>
@@ -2061,7 +2128,7 @@
         <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>15</v>
@@ -2073,7 +2140,7 @@
         <v>16</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
         <v>30</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2225,7 +2292,7 @@
         <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
@@ -2255,7 +2322,7 @@
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
@@ -2317,10 +2384,10 @@
         <v>41.4</v>
       </c>
       <c r="J11" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L11" t="n">
         <v>10.6</v>
@@ -2341,19 +2408,19 @@
         <v>0.772</v>
       </c>
       <c r="R11" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
       <c r="U11" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
         <v>9.5</v>
@@ -2365,19 +2432,19 @@
         <v>3.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB11" t="n">
         <v>109.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,13 +2456,13 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2404,7 +2471,7 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2419,13 +2486,13 @@
         <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2434,7 +2501,7 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -2443,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -2499,67 +2566,67 @@
         <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>11.5</v>
       </c>
       <c r="M12" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
         <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.727</v>
+        <v>0.721</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="S12" t="n">
         <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
         <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2595,37 +2662,37 @@
         <v>8</v>
       </c>
       <c r="AP12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR12" t="n">
         <v>6</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8</v>
       </c>
       <c r="AS12" t="n">
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>0.429</v>
+        <v>0.435</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,7 +2748,7 @@
         <v>36.5</v>
       </c>
       <c r="J13" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.438</v>
@@ -2690,34 +2757,34 @@
         <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N13" t="n">
         <v>0.339</v>
       </c>
       <c r="O13" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P13" t="n">
         <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T13" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U13" t="n">
         <v>21.4</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W13" t="n">
         <v>6.1</v>
@@ -2729,43 +2796,43 @@
         <v>4.9</v>
       </c>
       <c r="Z13" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA13" t="n">
         <v>21</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>21.1</v>
       </c>
       <c r="AB13" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF13" t="n">
         <v>20</v>
       </c>
-      <c r="AF13" t="n">
-        <v>21</v>
-      </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2780,37 +2847,37 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -2941,7 +3008,7 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2959,7 +3026,7 @@
         <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -2968,7 +3035,7 @@
         <v>28</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>21</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T15" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="U15" t="n">
         <v>20.9</v>
@@ -3087,25 +3154,25 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,7 +3187,7 @@
         <v>5</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
@@ -3135,22 +3202,22 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
@@ -3165,16 +3232,16 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA15" t="n">
         <v>22</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -3209,43 +3276,43 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
         <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>0.704</v>
+        <v>0.7</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M16" t="n">
         <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O16" t="n">
         <v>18.1</v>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q16" t="n">
         <v>0.776</v>
@@ -3266,7 +3333,7 @@
         <v>13.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X16" t="n">
         <v>4.3</v>
@@ -3281,13 +3348,13 @@
         <v>20.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3308,7 +3375,7 @@
         <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,19 +3384,19 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>16</v>
@@ -3344,13 +3411,13 @@
         <v>6</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV17" t="n">
         <v>20</v>
@@ -3532,16 +3599,16 @@
         <v>23</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>8</v>
       </c>
       <c r="BB17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3666,7 +3733,7 @@
         <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
@@ -3687,10 +3754,10 @@
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>19</v>
@@ -3699,13 +3766,13 @@
         <v>23</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW18" t="n">
         <v>4</v>
@@ -3717,16 +3784,16 @@
         <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -3755,37 +3822,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>0.229</v>
+        <v>0.217</v>
       </c>
       <c r="H19" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I19" t="n">
         <v>36.7</v>
       </c>
       <c r="J19" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
         <v>14.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0.336</v>
+        <v>0.331</v>
       </c>
       <c r="O19" t="n">
         <v>19.4</v>
@@ -3800,16 +3867,16 @@
         <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T19" t="n">
         <v>41.7</v>
       </c>
       <c r="U19" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
         <v>8.300000000000001</v>
@@ -3818,22 +3885,22 @@
         <v>3.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA19" t="n">
         <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.9</v>
+        <v>-8.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,7 +3912,7 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
         <v>22</v>
@@ -3863,16 +3930,16 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>4</v>
@@ -3905,7 +3972,7 @@
         <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
         <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>0.522</v>
+        <v>0.529</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,10 +4022,10 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>7.1</v>
@@ -3967,28 +4034,28 @@
         <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="O20" t="n">
         <v>16.6</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T20" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V20" t="n">
         <v>13.7</v>
@@ -3997,7 +4064,7 @@
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
@@ -4006,16 +4073,16 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
         <v>15</v>
@@ -4036,25 +4103,25 @@
         <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
@@ -4063,7 +4130,7 @@
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>0.197</v>
+        <v>0.2</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4137,31 +4204,31 @@
         <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K21" t="n">
         <v>0.429</v>
       </c>
       <c r="L21" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
         <v>19.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O21" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="P21" t="n">
         <v>19</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
@@ -4173,31 +4240,31 @@
         <v>21.4</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
         <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA21" t="n">
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4215,19 +4282,19 @@
         <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4245,7 +4312,7 @@
         <v>29</v>
       </c>
       <c r="AT21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU21" t="n">
         <v>18</v>
@@ -4257,10 +4324,10 @@
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>12</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4418,7 +4485,7 @@
         <v>8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4433,13 +4500,13 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW22" t="n">
         <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G23" t="n">
-        <v>0.31</v>
+        <v>0.306</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
         <v>82.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.353</v>
@@ -4525,43 +4592,43 @@
         <v>0.728</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U23" t="n">
         <v>20.6</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
         <v>7.9</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,7 +4646,7 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
@@ -4606,7 +4673,7 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
@@ -4621,10 +4688,10 @@
         <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4809,7 +4876,7 @@
         <v>26</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>18</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -4946,7 +5013,7 @@
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
         <v>8</v>
@@ -4958,13 +5025,13 @@
         <v>14</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -4973,16 +5040,16 @@
         <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5122,7 +5189,7 @@
         <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
         <v>8</v>
@@ -5137,13 +5204,13 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5337,7 +5404,7 @@
         <v>8</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" t="n">
         <v>25</v>
       </c>
       <c r="G28" t="n">
-        <v>0.632</v>
+        <v>0.638</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,10 +5478,10 @@
         <v>38.6</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
@@ -5423,13 +5490,13 @@
         <v>22.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="n">
         <v>0.776</v>
@@ -5438,16 +5505,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
         <v>7.9</v>
@@ -5465,16 +5532,16 @@
         <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.6</v>
+        <v>102.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF28" t="n">
         <v>6</v>
@@ -5489,7 +5556,7 @@
         <v>6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
@@ -5519,13 +5586,13 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>12</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE29" t="n">
         <v>10</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5671,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -5757,52 +5824,52 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>0.443</v>
+        <v>0.449</v>
       </c>
       <c r="H30" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I30" t="n">
         <v>35.3</v>
       </c>
       <c r="J30" t="n">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.448</v>
       </c>
       <c r="L30" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M30" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N30" t="n">
         <v>0.348</v>
       </c>
       <c r="O30" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P30" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.723</v>
+        <v>0.726</v>
       </c>
       <c r="R30" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T30" t="n">
         <v>43.7</v>
@@ -5826,16 +5893,16 @@
         <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC30" t="n">
         <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
         <v>18</v>
@@ -5865,7 +5932,7 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
         <v>16</v>
@@ -5874,16 +5941,16 @@
         <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,10 +5959,10 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
@@ -5907,7 +5974,7 @@
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
@@ -5939,46 +6006,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" t="n">
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.464</v>
+        <v>0.466</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O31" t="n">
         <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R31" t="n">
         <v>10.4</v>
@@ -5987,58 +6054,58 @@
         <v>33.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U31" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.2</v>
+        <v>98.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
       </c>
       <c r="AF31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH31" t="n">
         <v>13</v>
       </c>
-      <c r="AG31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>17</v>
-      </c>
       <c r="AI31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
         <v>23</v>
       </c>
       <c r="AK31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6059,7 +6126,7 @@
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
@@ -6071,19 +6138,19 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6092,7 +6159,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-23-2014-15</t>
+          <t>2015-03-23</t>
         </is>
       </c>
     </row>
